--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>90.83936964397128</v>
+        <v>14.76139756714533</v>
       </c>
       <c r="D2" t="n">
-        <v>29.54136904949666</v>
+        <v>4.800472470543208</v>
       </c>
       <c r="E2" t="n">
-        <v>17.75432449991238</v>
+        <v>2.885077731235762</v>
       </c>
       <c r="F2" t="n">
-        <v>14.32549529787353</v>
+        <v>2.327892985904449</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.48896593145197</v>
+        <v>9.666956963860946</v>
       </c>
       <c r="D3" t="n">
-        <v>59.70400194436793</v>
+        <v>9.701900315959788</v>
       </c>
       <c r="E3" t="n">
-        <v>17.75432449991238</v>
+        <v>2.885077731235762</v>
       </c>
       <c r="F3" t="n">
-        <v>14.32549529787353</v>
+        <v>2.327892985904449</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.22659049987808</v>
+        <v>8.486820956230188</v>
       </c>
       <c r="D4" t="n">
-        <v>51.98760307900614</v>
+        <v>8.447985500338499</v>
       </c>
       <c r="E4" t="n">
-        <v>17.75432449991238</v>
+        <v>2.885077731235762</v>
       </c>
       <c r="F4" t="n">
-        <v>14.32549529787353</v>
+        <v>2.327892985904449</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.79895828285197</v>
+        <v>11.17983072096345</v>
       </c>
       <c r="D5" t="n">
-        <v>67.99235296954633</v>
+        <v>11.04875735755128</v>
       </c>
       <c r="E5" t="n">
-        <v>17.75432449991238</v>
+        <v>2.885077731235762</v>
       </c>
       <c r="F5" t="n">
-        <v>14.32549529787353</v>
+        <v>2.327892985904449</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.51887468088211</v>
+        <v>9.184317135643344</v>
       </c>
       <c r="D6" t="n">
-        <v>57.32163073935826</v>
+        <v>9.314764995145717</v>
       </c>
       <c r="E6" t="n">
-        <v>17.75432449991238</v>
+        <v>2.885077731235762</v>
       </c>
       <c r="F6" t="n">
-        <v>14.32549529787353</v>
+        <v>2.327892985904449</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.89285294599749</v>
+        <v>5.182588603724593</v>
       </c>
       <c r="D7" t="n">
-        <v>31.61862633130241</v>
+        <v>5.138026778836642</v>
       </c>
       <c r="E7" t="n">
-        <v>17.75432449991238</v>
+        <v>2.885077731235762</v>
       </c>
       <c r="F7" t="n">
-        <v>14.32549529787353</v>
+        <v>2.327892985904449</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
